--- a/Hoja de cálculo sin título.xlsx
+++ b/Hoja de cálculo sin título.xlsx
@@ -36,6 +36,138 @@
     <t xml:space="preserve">Concejal</t>
   </si>
   <si>
+    <t xml:space="preserve">INSTITUTO SUPERIOR SANTA MARÍA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGUEZ EVELYN ANISIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRINIDAD VALERIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jair Dib</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instituto Madre de la Misericordia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbieri Anna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carvallo Thomas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laura Traid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instituto Superior Lisandro de la Torre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luciano Fabian Barrios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elias Joaquín Galarza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Eva Jiménez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escuela de Educación Técnica EPET 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croucciee Santino Horacio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vicente Ernestina Gianella </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luciana Scromeda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instituto Superior Colegio del Carmen (0437)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amarilla Barboza Maximiliano Ruben Hernando </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuñez Lara Valentina </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dardo Romero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOP 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samudio Antonela Noelia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obispo Mijail Alejandro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hector Cardozo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPET 36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antonella Mendez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benitez Agustina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mazal Malena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escuela Superior de Comercio N° 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARREIRO LAUTARO EZEQUIEL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villalba Anyelen Aimara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valeria GdO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instituto Proyección 2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candela Tomas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celeste Monserrath Vallejos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salom Judith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instituto Horacio Quiroga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varela Dalia Vanesa Mailen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DECHAT THEISEN ELIAS ANGEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samira Almiron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instituto Gutenberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victoria Correa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sofía Etchegoin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horacio Martinez</t>
+  </si>
+  <si>
     <t xml:space="preserve">EPET N 2</t>
   </si>
   <si>
@@ -46,42 +178,6 @@
   </si>
   <si>
     <t xml:space="preserve">Santiago Koch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSTITUTO SUPERIOR SANTA MARÍA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RODRIGUEZ EVELYN ANISIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRINIDAD VALERIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jair Dib</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instituto Superior Lisandro de la Torre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luciano Fabian Barrios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elias Joaquín Galarza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maria Eva Jiménez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escuela Superior de Comercio N° 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BARREIRO LAUTARO EZEQUIEL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villalba Anyelen Aimara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valeria GdO</t>
   </si>
   <si>
     <t xml:space="preserve">Benjamin Matienzo </t>
@@ -95,102 +191,6 @@
   </si>
   <si>
     <t xml:space="preserve">Argañaraz Pablo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOP 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samudio Antonela Noelia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obispo Mijail Alejandro </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hector Cardozo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instituto Proyección 2000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candela Tomas </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Celeste Monserrath Vallejos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salom Judith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPET 36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antonella Mendez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benitez Agustina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mazal Malena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instituto Superior Colegio del Carmen (0437)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amarilla Barboza Maximiliano Ruben Hernando </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuñez Lara Valentina </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dardo Romero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instituto Horacio Quiroga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varela Dalia Vanesa Mailen </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DECHAT THEISEN ELIAS ANGEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samira Almiron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instituto Gutenberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoria Correa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sofía Etchegoin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horacio Martinez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escuela de Educación Técnica EPET 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Croucciee Santino Horacio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vicente Ernestina Gianella </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luciana Scromeda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instituto Madre de la Misericordia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbieri Anna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carvallo Thomas </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laura Traid</t>
   </si>
   <si>
     <t xml:space="preserve">BOP N° 9</t>
@@ -332,7 +332,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -375,21 +375,6 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFF8F9FA"/>
-      </left>
-      <right style="thin">
         <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
@@ -402,22 +387,7 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FF442F65"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
         <color rgb="FFF8F9FA"/>
@@ -442,6 +412,36 @@
       </top>
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -475,36 +475,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FF442F65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFF8F9FA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -531,7 +501,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -584,7 +554,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -592,23 +562,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -734,8 +692,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla_1" displayName="Tabla_1" ref="A1:D39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:D39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla_1" displayName="Tabla_1" ref="A1:D40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:D40"/>
   <tableColumns count="4">
     <tableColumn id="1" name="INSTITUCIÓN EDUCATIVA:"/>
     <tableColumn id="2" name="DATOS CONCEJAL ESTUDIANTIL TITULAR.&#10;NOMBRE Y APELLIDO:"/>
@@ -750,7 +708,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.25"/>
@@ -787,7 +745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
         <v>8</v>
       </c>
@@ -801,8 +759,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -811,12 +769,12 @@
       <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -825,26 +783,26 @@
       <c r="C5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -853,11 +811,11 @@
       <c r="C7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
@@ -871,8 +829,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -881,26 +839,26 @@
       <c r="C9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -909,12 +867,12 @@
       <c r="C11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -923,40 +881,40 @@
       <c r="C12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="5" t="s">
         <v>50</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>56</v>
       </c>
       <c r="B15" s="9" t="s">
@@ -965,12 +923,12 @@
       <c r="C15" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
         <v>60</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -979,12 +937,12 @@
       <c r="C16" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="7" t="s">
         <v>64</v>
       </c>
       <c r="B17" s="9" t="s">
@@ -993,12 +951,12 @@
       <c r="C17" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="5" t="s">
@@ -1007,12 +965,12 @@
       <c r="C18" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="8" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
         <v>72</v>
       </c>
       <c r="B19" s="12" t="s">
@@ -1021,324 +979,265 @@
       <c r="C19" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="13"/>
-    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="14"/>
-      <c r="D21" s="15"/>
+      <c r="D21" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="16"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="15"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15"/>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D23" s="16"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="16"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7"/>
-      <c r="D25" s="15"/>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="16"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7"/>
-      <c r="D27" s="15"/>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="16"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7"/>
-      <c r="D29" s="15"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="16"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7"/>
-      <c r="D31" s="15"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="16"/>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7"/>
-      <c r="D33" s="15"/>
-    </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4"/>
-      <c r="D34" s="17"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="15"/>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4"/>
-      <c r="D36" s="17"/>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7"/>
-      <c r="D37" s="15"/>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4"/>
-      <c r="D38" s="17"/>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18"/>
-      <c r="B39" s="9"/>
-      <c r="D39" s="19"/>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C40" s="20"/>
-    </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C41" s="20"/>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C42" s="20"/>
-    </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C43" s="20"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="16"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C43" s="17"/>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C44" s="20"/>
+      <c r="C44" s="17"/>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C45" s="20"/>
+      <c r="C45" s="17"/>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C46" s="20"/>
+      <c r="C46" s="17"/>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C47" s="20"/>
+      <c r="C47" s="17"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C48" s="20"/>
+      <c r="C48" s="17"/>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C49" s="20"/>
+      <c r="C49" s="17"/>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C50" s="20"/>
+      <c r="C50" s="17"/>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C51" s="20"/>
+      <c r="C51" s="17"/>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C52" s="20"/>
+      <c r="C52" s="17"/>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="20"/>
+      <c r="C53" s="17"/>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="20"/>
+      <c r="C54" s="17"/>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="20"/>
+      <c r="C55" s="17"/>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C56" s="20"/>
+      <c r="C56" s="17"/>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C57" s="20"/>
+      <c r="C57" s="17"/>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C58" s="20"/>
+      <c r="C58" s="17"/>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C59" s="20"/>
+      <c r="C59" s="17"/>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C60" s="20"/>
+      <c r="C60" s="17"/>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C61" s="20"/>
+      <c r="C61" s="17"/>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C62" s="20"/>
+      <c r="C62" s="17"/>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C63" s="20"/>
+      <c r="C63" s="17"/>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C64" s="20"/>
+      <c r="C64" s="17"/>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C65" s="20"/>
+      <c r="C65" s="17"/>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C66" s="20"/>
+      <c r="C66" s="17"/>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C67" s="20"/>
+      <c r="C67" s="17"/>
     </row>
     <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C68" s="20"/>
+      <c r="C68" s="17"/>
     </row>
     <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C69" s="20"/>
+      <c r="C69" s="17"/>
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C70" s="20"/>
+      <c r="C70" s="17"/>
     </row>
     <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C71" s="20"/>
+      <c r="C71" s="17"/>
     </row>
     <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C72" s="20"/>
+      <c r="C72" s="17"/>
     </row>
     <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C73" s="20"/>
+      <c r="C73" s="17"/>
     </row>
     <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C74" s="20"/>
+      <c r="C74" s="17"/>
     </row>
     <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C75" s="20"/>
+      <c r="C75" s="17"/>
     </row>
     <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C76" s="20"/>
+      <c r="C76" s="17"/>
     </row>
     <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C77" s="20"/>
+      <c r="C77" s="17"/>
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C78" s="20"/>
+      <c r="C78" s="17"/>
     </row>
     <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C79" s="20"/>
+      <c r="C79" s="17"/>
     </row>
     <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C80" s="20"/>
+      <c r="C80" s="17"/>
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C81" s="20"/>
+      <c r="C81" s="17"/>
     </row>
     <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C82" s="20"/>
+      <c r="C82" s="17"/>
     </row>
     <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C83" s="20"/>
+      <c r="C83" s="17"/>
     </row>
     <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C84" s="20"/>
+      <c r="C84" s="17"/>
     </row>
     <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C85" s="20"/>
+      <c r="C85" s="17"/>
     </row>
     <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C86" s="20"/>
+      <c r="C86" s="17"/>
     </row>
     <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C87" s="20"/>
+      <c r="C87" s="17"/>
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C88" s="20"/>
+      <c r="C88" s="17"/>
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C89" s="20"/>
+      <c r="C89" s="17"/>
     </row>
     <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C90" s="20"/>
+      <c r="C90" s="17"/>
     </row>
     <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C91" s="20"/>
+      <c r="C91" s="17"/>
     </row>
     <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C92" s="20"/>
+      <c r="C92" s="17"/>
     </row>
     <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C93" s="20"/>
+      <c r="C93" s="17"/>
     </row>
     <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C94" s="20"/>
+      <c r="C94" s="17"/>
     </row>
     <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C95" s="20"/>
+      <c r="C95" s="17"/>
     </row>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C96" s="20"/>
+      <c r="C96" s="17"/>
     </row>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C97" s="20"/>
+      <c r="C97" s="17"/>
     </row>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C98" s="20"/>
+      <c r="C98" s="17"/>
     </row>
     <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C99" s="20"/>
+      <c r="C99" s="17"/>
     </row>
     <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C100" s="20"/>
+      <c r="C100" s="17"/>
     </row>
     <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C101" s="20"/>
+      <c r="C101" s="17"/>
     </row>
     <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C102" s="20"/>
+      <c r="C102" s="17"/>
     </row>
     <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C103" s="20"/>
+      <c r="C103" s="17"/>
     </row>
     <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C104" s="20"/>
+      <c r="C104" s="17"/>
     </row>
     <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C105" s="20"/>
+      <c r="C105" s="17"/>
     </row>
     <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C106" s="20"/>
+      <c r="C106" s="17"/>
     </row>
     <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C107" s="20"/>
+      <c r="C107" s="17"/>
     </row>
     <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C108" s="20"/>
+      <c r="C108" s="17"/>
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C109" s="20"/>
+      <c r="C109" s="17"/>
     </row>
     <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C110" s="20"/>
+      <c r="C110" s="17"/>
     </row>
     <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C111" s="20"/>
+      <c r="C111" s="17"/>
     </row>
     <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C112" s="20"/>
+      <c r="C112" s="17"/>
     </row>
     <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C113" s="20"/>
+      <c r="C113" s="17"/>
+    </row>
+    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C114" s="17"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
